--- a/data/planilha_vendas_tratada.xlsx
+++ b/data/planilha_vendas_tratada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempJornada\Claude\AnaliseDeDados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2B61D4-7C93-4968-9C89-3520A1EFAFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF27558D-E786-4CDA-8547-9D4FA74ACF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Pendências" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Log de Correções'!$A$1:$E$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Log de Correções'!$A$1:$F$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vendas Tratadas'!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="228">
   <si>
     <t>ID Pedido</t>
   </si>
@@ -270,6 +270,9 @@
     <t>Regra Aplicada</t>
   </si>
   <si>
+    <t>Categoria</t>
+  </si>
+  <si>
     <t>Receita</t>
   </si>
   <si>
@@ -282,6 +285,9 @@
     <t>Texto convertido em número</t>
   </si>
   <si>
+    <t>Receita como texto</t>
+  </si>
+  <si>
     <t>2024-01-22</t>
   </si>
   <si>
@@ -291,12 +297,18 @@
     <t>Data convertida para DD/MM/AAAA</t>
   </si>
   <si>
+    <t>Data em formato não padrão</t>
+  </si>
+  <si>
     <t>maria souza</t>
   </si>
   <si>
     <t>Capitalização padronizada</t>
   </si>
   <si>
+    <t>Capitalização fora do padrão</t>
+  </si>
+  <si>
     <t>R$ 1150.00</t>
   </si>
   <si>
@@ -309,6 +321,9 @@
     <t>Grafia padronizada para lista oficial</t>
   </si>
   <si>
+    <t>Região fora do padrão</t>
+  </si>
+  <si>
     <t>sara jorge</t>
   </si>
   <si>
@@ -354,6 +369,9 @@
     <t>Duplicado exato do pedido 1001</t>
   </si>
   <si>
+    <t>Duplicado exato</t>
+  </si>
+  <si>
     <t>duplicado</t>
   </si>
   <si>
@@ -363,6 +381,9 @@
     <t>Marcação de qualidade removida (tratada em Alertas/Log)</t>
   </si>
   <si>
+    <t>Marcador de erro em Observações</t>
+  </si>
+  <si>
     <t>R$ 3750.00</t>
   </si>
   <si>
@@ -372,6 +393,9 @@
     <t>Inferida: Tomás Bastos atua apenas em Centro-Oeste</t>
   </si>
   <si>
+    <t>Campo vazio preenchido</t>
+  </si>
+  <si>
     <t>2024-02-20</t>
   </si>
   <si>
@@ -390,6 +414,9 @@
     <t>Status recuperado da coluna Observações</t>
   </si>
   <si>
+    <t>Status na coluna errada</t>
+  </si>
+  <si>
     <t>3 março 2024</t>
   </si>
   <si>
@@ -526,6 +553,9 @@
   </si>
   <si>
     <t>Traduzido para português</t>
+  </si>
+  <si>
+    <t>Status em outro idioma</t>
   </si>
   <si>
     <t>R$ 3400.00</t>
@@ -2189,16 +2219,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2214,25 +2245,31 @@
       <c r="E1" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>1001</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>1002</v>
       </c>
@@ -2240,16 +2277,19 @@
         <v>4</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>1002</v>
       </c>
@@ -2257,33 +2297,39 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>1002</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>1002</v>
       </c>
@@ -2291,16 +2337,19 @@
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>1002</v>
       </c>
@@ -2308,16 +2357,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>1002</v>
       </c>
@@ -2325,16 +2377,19 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>1003</v>
       </c>
@@ -2342,16 +2397,19 @@
         <v>4</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>1003</v>
       </c>
@@ -2359,33 +2417,39 @@
         <v>1</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>1003</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>1003</v>
       </c>
@@ -2393,16 +2457,19 @@
         <v>2</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>1003</v>
       </c>
@@ -2410,50 +2477,59 @@
         <v>3</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>1004</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>1005</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>1005</v>
       </c>
@@ -2461,50 +2537,59 @@
         <v>8</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>1005</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>1006</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>1006</v>
       </c>
@@ -2512,16 +2597,19 @@
         <v>2</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>1007</v>
       </c>
@@ -2529,16 +2617,19 @@
         <v>4</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>1007</v>
       </c>
@@ -2546,33 +2637,39 @@
         <v>1</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>29</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>1007</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>1007</v>
       </c>
@@ -2580,16 +2677,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>1008</v>
       </c>
@@ -2597,16 +2697,19 @@
         <v>4</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>1008</v>
       </c>
@@ -2614,33 +2717,39 @@
         <v>1</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>31</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>1008</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>1008</v>
       </c>
@@ -2648,16 +2757,19 @@
         <v>3</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>33</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>1009</v>
       </c>
@@ -2665,16 +2777,19 @@
         <v>8</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>1010</v>
       </c>
@@ -2682,16 +2797,19 @@
         <v>4</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>1010</v>
       </c>
@@ -2699,33 +2817,39 @@
         <v>1</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>1010</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>1010</v>
       </c>
@@ -2733,33 +2857,39 @@
         <v>3</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>1011</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>1011</v>
       </c>
@@ -2767,16 +2897,19 @@
         <v>7</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>1012</v>
       </c>
@@ -2784,16 +2917,19 @@
         <v>4</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>1012</v>
       </c>
@@ -2801,33 +2937,39 @@
         <v>1</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>1012</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>1012</v>
       </c>
@@ -2835,16 +2977,19 @@
         <v>2</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>1012</v>
       </c>
@@ -2852,33 +2997,39 @@
         <v>3</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>33</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>1013</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>1014</v>
       </c>
@@ -2886,16 +3037,19 @@
         <v>4</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>1014</v>
       </c>
@@ -2903,16 +3057,19 @@
         <v>1</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>31</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>1014</v>
       </c>
@@ -2920,67 +3077,79 @@
         <v>8</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>1014</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>1015</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>1016</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>1016</v>
       </c>
@@ -2988,16 +3157,19 @@
         <v>2</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>1017</v>
       </c>
@@ -3005,16 +3177,19 @@
         <v>4</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>1017</v>
       </c>
@@ -3022,33 +3197,39 @@
         <v>1</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>22</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>1017</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>1017</v>
       </c>
@@ -3056,33 +3237,39 @@
         <v>3</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>1018</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>1019</v>
       </c>
@@ -3090,16 +3277,19 @@
         <v>4</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>1019</v>
       </c>
@@ -3107,33 +3297,39 @@
         <v>1</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>47</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>1019</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>1019</v>
       </c>
@@ -3141,16 +3337,19 @@
         <v>2</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>1019</v>
       </c>
@@ -3158,16 +3357,19 @@
         <v>3</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>1019</v>
       </c>
@@ -3175,33 +3377,39 @@
         <v>7</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>1020</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>1021</v>
       </c>
@@ -3209,16 +3417,19 @@
         <v>8</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>1022</v>
       </c>
@@ -3226,16 +3437,19 @@
         <v>4</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>1022</v>
       </c>
@@ -3243,33 +3457,39 @@
         <v>1</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>1022</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>1022</v>
       </c>
@@ -3277,16 +3497,19 @@
         <v>2</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>1022</v>
       </c>
@@ -3294,33 +3517,39 @@
         <v>3</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>1023</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>1024</v>
       </c>
@@ -3328,33 +3557,39 @@
         <v>4</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>1024</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>1025</v>
       </c>
@@ -3362,33 +3597,39 @@
         <v>1</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>29</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>1025</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>1026</v>
       </c>
@@ -3396,16 +3637,19 @@
         <v>4</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>1026</v>
       </c>
@@ -3413,33 +3657,39 @@
         <v>1</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>36</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>1026</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>1026</v>
       </c>
@@ -3447,16 +3697,19 @@
         <v>7</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>1027</v>
       </c>
@@ -3464,33 +3717,39 @@
         <v>8</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>1027</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>1027</v>
       </c>
@@ -3498,33 +3757,39 @@
         <v>3</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>1028</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>1029</v>
       </c>
@@ -3532,16 +3797,19 @@
         <v>4</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>1029</v>
       </c>
@@ -3549,16 +3817,19 @@
         <v>1</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D80" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>1029</v>
       </c>
@@ -3566,33 +3837,39 @@
         <v>8</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>1029</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>1029</v>
       </c>
@@ -3600,16 +3877,19 @@
         <v>2</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>1030</v>
       </c>
@@ -3617,16 +3897,19 @@
         <v>4</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>1030</v>
       </c>
@@ -3634,33 +3917,39 @@
         <v>1</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>1030</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>1030</v>
       </c>
@@ -3668,16 +3957,19 @@
         <v>2</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>1030</v>
       </c>
@@ -3685,17 +3977,20 @@
         <v>3</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E88" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:F88" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3714,114 +4009,114 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E2" s="17"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E7" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
